--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CÍRCULO GIJÓN BALONCESTO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CÍRCULO GIJÓN BALONCESTO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>12.9795</v>
+        <v>2.4767</v>
       </c>
       <c r="E2" t="n">
-        <v>17.2119</v>
+        <v>-3.867500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.231999999999999</v>
+        <v>6.3443</v>
       </c>
       <c r="G2" t="n">
-        <v>-40.7834</v>
+        <v>-1.5868</v>
       </c>
       <c r="H2" t="n">
-        <v>-32.6429</v>
+        <v>-7.5259</v>
       </c>
       <c r="I2" t="n">
-        <v>-8.1403</v>
+        <v>5.9394</v>
       </c>
       <c r="J2" t="n">
-        <v>10.5101</v>
+        <v>16.2564</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7097</v>
+        <v>7.664</v>
       </c>
       <c r="L2" t="n">
-        <v>8.8002</v>
+        <v>8.592700000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-51.2933</v>
+        <v>-17.8433</v>
       </c>
       <c r="N2" t="n">
-        <v>-34.3532</v>
+        <v>-15.1901</v>
       </c>
       <c r="O2" t="n">
-        <v>-16.9403</v>
+        <v>-2.6531</v>
       </c>
       <c r="P2" t="n">
-        <v>12.2793</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q2" t="n">
-        <v>-38.9183</v>
+        <v>-22.685</v>
       </c>
       <c r="R2" t="n">
-        <v>51.1972</v>
+        <v>21.6445</v>
       </c>
       <c r="S2" t="n">
-        <v>51.8817</v>
+        <v>-0.2453</v>
       </c>
       <c r="T2" t="n">
-        <v>32.1403</v>
+        <v>-2.3039</v>
       </c>
       <c r="U2" t="n">
-        <v>19.7418</v>
+        <v>2.0585</v>
       </c>
       <c r="V2" t="n">
-        <v>-10.3981</v>
+        <v>5.3495</v>
       </c>
       <c r="W2" t="n">
-        <v>13.4798</v>
+        <v>4.8649</v>
       </c>
       <c r="X2" t="n">
-        <v>-23.8779</v>
+        <v>0.4846</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TSEGAKELE</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9902</v>
+        <v>0.2890999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7229</v>
+        <v>33.723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2674000000000001</v>
+        <v>-33.4339</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.5221</v>
+        <v>10.1379</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.3872</v>
+        <v>-10.9976</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.1349</v>
+        <v>21.1354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5581</v>
+        <v>62.3986</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4911</v>
+        <v>23.404</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0492</v>
+        <v>38.9942</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.0799</v>
+        <v>-52.2609</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.8959</v>
+        <v>-34.4021</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.1842</v>
+        <v>-17.8587</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2486</v>
+        <v>-15.609</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9.781599999999999</v>
+        <v>-69.9281</v>
       </c>
       <c r="R3" t="n">
-        <v>11.0301</v>
+        <v>54.3188</v>
       </c>
       <c r="S3" t="n">
-        <v>7.787000000000001</v>
+        <v>-14.0381</v>
       </c>
       <c r="T3" t="n">
-        <v>6.754099999999999</v>
+        <v>-9.6409</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0331</v>
+        <v>-4.3968</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4766</v>
+        <v>19.7985</v>
       </c>
       <c r="W3" t="n">
-        <v>4.192600000000001</v>
+        <v>50.8937</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7161</v>
+        <v>-31.0952</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.7681</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0311</v>
+        <v>-0.8168</v>
       </c>
       <c r="F4" t="n">
         <v>0.04870000000000002</v>
@@ -766,10 +766,10 @@
         <v>0.6243000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2081</v>
+        <v>0.006200000000000011</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.292</v>
       </c>
       <c r="U4" t="n">
         <v>-0.2857</v>
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3895</v>
+        <v>-1.3602</v>
       </c>
       <c r="E5" t="n">
         <v>-1.2363</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1533</v>
+        <v>-0.124</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2409</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4618</v>
+        <v>-0.4325</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2661</v>
+        <v>-0.2368</v>
       </c>
       <c r="V5" t="n">
         <v>0.3538</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>A. TSEGAKELE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.85</v>
+        <v>-3.7059</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.609100000000001</v>
+        <v>-3.7189</v>
       </c>
       <c r="F6" t="n">
-        <v>3.758700000000001</v>
+        <v>0.01300000000000034</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5868</v>
+        <v>-9.5221</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.5259</v>
+        <v>-6.3872</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9394</v>
+        <v>-3.1349</v>
       </c>
       <c r="J6" t="n">
-        <v>16.2564</v>
+        <v>0.5581</v>
       </c>
       <c r="K6" t="n">
-        <v>7.664</v>
+        <v>-0.4911</v>
       </c>
       <c r="L6" t="n">
-        <v>8.592700000000001</v>
+        <v>1.0492</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.8433</v>
+        <v>-10.0799</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.1901</v>
+        <v>-5.8959</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.6531</v>
+        <v>-4.1842</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0406</v>
+        <v>1.2486</v>
       </c>
       <c r="Q6" t="n">
-        <v>-22.685</v>
+        <v>-9.781599999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>21.6445</v>
+        <v>11.0301</v>
       </c>
       <c r="S6" t="n">
-        <v>-6.5724</v>
+        <v>2.0909</v>
       </c>
       <c r="T6" t="n">
-        <v>-6.0454</v>
+        <v>1.3124</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.527</v>
+        <v>0.7787000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3495</v>
+        <v>2.4766</v>
       </c>
       <c r="W6" t="n">
-        <v>4.8649</v>
+        <v>4.192600000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4846</v>
+        <v>-1.7161</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.159200000000001</v>
+        <v>-6.2242</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8472</v>
+        <v>-1.1997</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.3121</v>
+        <v>-5.0246</v>
       </c>
       <c r="G7" t="n">
         <v>-6.4809</v>
@@ -1000,13 +1000,13 @@
         <v>9.989799999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1531</v>
+        <v>-2.2177</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.6294</v>
+        <v>-0.9818000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5233999999999999</v>
+        <v>-1.2359</v>
       </c>
       <c r="V7" t="n">
         <v>-4.1854</v>
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.176</v>
+        <v>-6.799899999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.6145</v>
+        <v>-5.150399999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5615</v>
+        <v>-1.6495</v>
       </c>
       <c r="G8" t="n">
         <v>-7.8175</v>
@@ -1078,13 +1078,13 @@
         <v>1.0405</v>
       </c>
       <c r="S8" t="n">
-        <v>1.811</v>
+        <v>1.1872</v>
       </c>
       <c r="T8" t="n">
-        <v>1.475</v>
+        <v>0.9391</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3361</v>
+        <v>0.248</v>
       </c>
       <c r="V8" t="n">
         <v>1.0791</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.3507</v>
+        <v>-10.2663</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0945</v>
+        <v>-1.6725</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.2563</v>
+        <v>-8.594200000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-11.393</v>
+        <v>1.493</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.4899</v>
+        <v>0.5278999999999995</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9031</v>
+        <v>0.9651000000000005</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7078000000000002</v>
+        <v>25.5422</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0579</v>
+        <v>16.7519</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3502000000000001</v>
+        <v>8.790199999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.6851</v>
+        <v>-24.0492</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.431799999999999</v>
+        <v>-16.2242</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2533</v>
+        <v>-7.825299999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2488</v>
+        <v>3.3299</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.3248</v>
+        <v>-28.9286</v>
       </c>
       <c r="R9" t="n">
-        <v>9.573399999999999</v>
+        <v>32.2583</v>
       </c>
       <c r="S9" t="n">
-        <v>6.4717</v>
+        <v>-11.7001</v>
       </c>
       <c r="T9" t="n">
-        <v>6.2658</v>
+        <v>-6.0517</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2058999999999999</v>
+        <v>-5.6479</v>
       </c>
       <c r="V9" t="n">
-        <v>-5.6784</v>
+        <v>-3.3893</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6722999999999999</v>
+        <v>7.7659</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.350700000000001</v>
+        <v>-11.1551</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>-18.6238</v>
+        <v>-15.2714</v>
       </c>
       <c r="E10" t="n">
-        <v>20.7149</v>
+        <v>-7.4708</v>
       </c>
       <c r="F10" t="n">
-        <v>-39.3388</v>
+        <v>-7.800400000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>10.1379</v>
+        <v>-11.393</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.9976</v>
+        <v>-9.4899</v>
       </c>
       <c r="I10" t="n">
-        <v>21.1354</v>
+        <v>-1.9031</v>
       </c>
       <c r="J10" t="n">
-        <v>62.3986</v>
+        <v>-0.7078000000000002</v>
       </c>
       <c r="K10" t="n">
-        <v>23.404</v>
+        <v>-1.0579</v>
       </c>
       <c r="L10" t="n">
-        <v>38.9942</v>
+        <v>0.3502000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-52.2609</v>
+        <v>-10.6851</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.4021</v>
+        <v>-8.431799999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-17.8587</v>
+        <v>-2.2533</v>
       </c>
       <c r="P10" t="n">
-        <v>-15.609</v>
+        <v>1.2488</v>
       </c>
       <c r="Q10" t="n">
-        <v>-69.9281</v>
+        <v>-8.3248</v>
       </c>
       <c r="R10" t="n">
-        <v>54.3188</v>
+        <v>9.573399999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-32.9509</v>
+        <v>0.5514999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-22.6495</v>
+        <v>0.8895</v>
       </c>
       <c r="U10" t="n">
-        <v>-10.3017</v>
+        <v>-0.3383</v>
       </c>
       <c r="V10" t="n">
-        <v>19.7985</v>
+        <v>-5.6784</v>
       </c>
       <c r="W10" t="n">
-        <v>50.8937</v>
+        <v>0.6722999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-31.0952</v>
+        <v>-6.350700000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-21.6777</v>
+        <v>-16.031</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8599</v>
+        <v>-3.046</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.8176</v>
+        <v>-12.9853</v>
       </c>
       <c r="G11" t="n">
         <v>-22.4863</v>
@@ -1312,13 +1312,13 @@
         <v>26.0145</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.1301</v>
+        <v>-4.4838</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.1721</v>
+        <v>-1.3581</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.9578</v>
+        <v>-3.1257</v>
       </c>
       <c r="V11" t="n">
         <v>-5.9189</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-23.5063</v>
+        <v>-21.7335</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.9783</v>
+        <v>-11.7511</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.5281</v>
+        <v>-9.982100000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.9873</v>
+        <v>-23.7959</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.3475</v>
+        <v>-11.3528</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6398000000000004</v>
+        <v>-12.4435</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3716</v>
+        <v>20.2415</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8594999999999999</v>
+        <v>15.8625</v>
       </c>
       <c r="L12" t="n">
-        <v>6.5119</v>
+        <v>4.3787</v>
       </c>
       <c r="M12" t="n">
-        <v>-21.359</v>
+        <v>-44.0373</v>
       </c>
       <c r="N12" t="n">
-        <v>-14.2072</v>
+        <v>-27.2154</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.1518</v>
+        <v>-16.822</v>
       </c>
       <c r="P12" t="n">
-        <v>5.2029</v>
+        <v>-13.944</v>
       </c>
       <c r="Q12" t="n">
-        <v>-32.4666</v>
+        <v>-58.6895</v>
       </c>
       <c r="R12" t="n">
-        <v>37.6692</v>
+        <v>44.7454</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2798999999999999</v>
+        <v>-6.9587</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1835</v>
+        <v>-6.047</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4634</v>
+        <v>-0.9115</v>
       </c>
       <c r="V12" t="n">
-        <v>-14.4421</v>
+        <v>22.9648</v>
       </c>
       <c r="W12" t="n">
-        <v>8.933400000000001</v>
+        <v>32.7439</v>
       </c>
       <c r="X12" t="n">
-        <v>-23.3753</v>
+        <v>-9.779</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.4969</v>
+        <v>-24.3427</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.8432</v>
+        <v>-9.3393</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.6539</v>
+        <v>-15.0033</v>
       </c>
       <c r="G13" t="n">
-        <v>1.493</v>
+        <v>-40.7834</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5278999999999995</v>
+        <v>-32.6429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9651000000000005</v>
+        <v>-8.1403</v>
       </c>
       <c r="J13" t="n">
-        <v>25.5422</v>
+        <v>10.5101</v>
       </c>
       <c r="K13" t="n">
-        <v>16.7519</v>
+        <v>1.7097</v>
       </c>
       <c r="L13" t="n">
-        <v>8.790199999999999</v>
+        <v>8.8002</v>
       </c>
       <c r="M13" t="n">
-        <v>-24.0492</v>
+        <v>-51.2933</v>
       </c>
       <c r="N13" t="n">
-        <v>-16.2242</v>
+        <v>-34.3532</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.825299999999999</v>
+        <v>-16.9403</v>
       </c>
       <c r="P13" t="n">
-        <v>3.3299</v>
+        <v>12.2793</v>
       </c>
       <c r="Q13" t="n">
-        <v>-28.9286</v>
+        <v>-38.9183</v>
       </c>
       <c r="R13" t="n">
-        <v>32.2583</v>
+        <v>51.1972</v>
       </c>
       <c r="S13" t="n">
-        <v>-27.9303</v>
+        <v>14.5601</v>
       </c>
       <c r="T13" t="n">
-        <v>-16.2225</v>
+        <v>5.589100000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-11.7081</v>
+        <v>8.970599999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.3893</v>
+        <v>-10.3981</v>
       </c>
       <c r="W13" t="n">
-        <v>7.7659</v>
+        <v>13.4798</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.1551</v>
+        <v>-23.8779</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.5503</v>
+        <v>-27.3522</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.0587</v>
+        <v>-16.8567</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.4918</v>
+        <v>-10.4951</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.7959</v>
+        <v>-13.9873</v>
       </c>
       <c r="H14" t="n">
-        <v>-11.3528</v>
+        <v>-13.3475</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.4435</v>
+        <v>-0.6398000000000004</v>
       </c>
       <c r="J14" t="n">
-        <v>20.2415</v>
+        <v>7.3716</v>
       </c>
       <c r="K14" t="n">
-        <v>15.8625</v>
+        <v>0.8594999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3787</v>
+        <v>6.5119</v>
       </c>
       <c r="M14" t="n">
-        <v>-44.0373</v>
+        <v>-21.359</v>
       </c>
       <c r="N14" t="n">
-        <v>-27.2154</v>
+        <v>-14.2072</v>
       </c>
       <c r="O14" t="n">
-        <v>-16.822</v>
+        <v>-7.1518</v>
       </c>
       <c r="P14" t="n">
-        <v>-13.944</v>
+        <v>5.2029</v>
       </c>
       <c r="Q14" t="n">
-        <v>-58.6895</v>
+        <v>-32.4666</v>
       </c>
       <c r="R14" t="n">
-        <v>44.7454</v>
+        <v>37.6692</v>
       </c>
       <c r="S14" t="n">
-        <v>-21.7755</v>
+        <v>-4.1258</v>
       </c>
       <c r="T14" t="n">
-        <v>-17.3547</v>
+        <v>-0.6954999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.421</v>
+        <v>-3.4303</v>
       </c>
       <c r="V14" t="n">
-        <v>22.9648</v>
+        <v>-14.4421</v>
       </c>
       <c r="W14" t="n">
-        <v>32.7439</v>
+        <v>8.933400000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.779</v>
+        <v>-23.3753</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-48.6268</v>
+        <v>-29.4027</v>
       </c>
       <c r="E15" t="n">
-        <v>-20.2838</v>
+        <v>-8.822500000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>-28.3427</v>
+        <v>-20.5803</v>
       </c>
       <c r="G15" t="n">
         <v>-7.391200000000001</v>
@@ -1624,13 +1624,13 @@
         <v>39.9586</v>
       </c>
       <c r="S15" t="n">
-        <v>-30.7692</v>
+        <v>-11.5449</v>
       </c>
       <c r="T15" t="n">
-        <v>-18.9141</v>
+        <v>-7.452500000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-11.8551</v>
+        <v>-4.0925</v>
       </c>
       <c r="V15" t="n">
         <v>-14.4208</v>
@@ -1657,13 +1657,13 @@
         <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>-53.9743</v>
+        <v>-58.1549</v>
       </c>
       <c r="E16" t="n">
-        <v>-40.3021</v>
+        <v>-43.4237</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.6722</v>
+        <v>-14.7314</v>
       </c>
       <c r="G16" t="n">
         <v>-34.8762</v>
@@ -1702,13 +1702,13 @@
         <v>23.1011</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2442</v>
+        <v>-0.9359999999999998</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6070000000000001</v>
+        <v>-2.5144</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6372</v>
+        <v>1.5784</v>
       </c>
       <c r="V16" t="n">
         <v>-5.9013</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-242.3942</v>
+        <v>-218.6472</v>
       </c>
       <c r="E17" t="n">
-        <v>-94.10899999999999</v>
+        <v>-84.64920000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-148.2855</v>
+        <v>-133.9981</v>
       </c>
       <c r="G17" t="n">
         <v>-169.0887</v>
@@ -1762,7 +1762,7 @@
         <v>81.7016</v>
       </c>
       <c r="M17" t="n">
-        <v>-327.3051</v>
+        <v>-327.3050999999999</v>
       </c>
       <c r="N17" t="n">
         <v>-209.3559</v>
@@ -1774,19 +1774,19 @@
         <v>1.040499999999994</v>
       </c>
       <c r="Q17" t="n">
-        <v>-362.1272999999999</v>
+        <v>-362.1273</v>
       </c>
       <c r="R17" t="n">
-        <v>363.1656999999999</v>
+        <v>363.1657</v>
       </c>
       <c r="S17" t="n">
-        <v>-62.0357</v>
+        <v>-38.287</v>
       </c>
       <c r="T17" t="n">
-        <v>-37.67999999999999</v>
+        <v>-28.2194</v>
       </c>
       <c r="U17" t="n">
-        <v>-24.3552</v>
+        <v>-10.0672</v>
       </c>
       <c r="V17" t="n">
         <v>-12.312</v>
